--- a/Config.xlsx
+++ b/Config.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE69A421-B0B7-43F7-A941-E94AD1A40388}"/>
   <bookViews>
-    <workbookView xWindow="30540" yWindow="0" windowWidth="21165" windowHeight="20985" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1458,15 +1458,15 @@
         <v>232.8</v>
       </c>
       <c r="D15" s="1">
-        <f>D14</f>
+        <f t="shared" ref="D15:F16" si="2">D14</f>
         <v>748.1</v>
       </c>
       <c r="E15" s="1">
-        <f>E14</f>
+        <f t="shared" si="2"/>
         <v>85.7</v>
       </c>
       <c r="F15" s="1">
-        <f>F14</f>
+        <f t="shared" si="2"/>
         <v>125.4</v>
       </c>
       <c r="G15" s="1">
@@ -1516,15 +1516,15 @@
         <v>328.5</v>
       </c>
       <c r="D16" s="1">
-        <f>D15</f>
+        <f t="shared" si="2"/>
         <v>748.1</v>
       </c>
       <c r="E16" s="1">
-        <f>E15</f>
+        <f t="shared" si="2"/>
         <v>85.7</v>
       </c>
       <c r="F16" s="1">
-        <f>F15</f>
+        <f t="shared" si="2"/>
         <v>125.4</v>
       </c>
       <c r="G16" s="1">

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE69A421-B0B7-43F7-A941-E94AD1A40388}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA2A6892-6EE2-460E-8E52-BAF359F83BFE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="29040" yWindow="3195" windowWidth="21600" windowHeight="13545" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -147,33 +147,18 @@
     <t>5A</t>
   </si>
   <si>
-    <t>WARRIORS_PITCH_5A.png</t>
-  </si>
-  <si>
     <t>5B</t>
   </si>
   <si>
-    <t>WARRIORS_PITCH_5B.png</t>
-  </si>
-  <si>
     <t>5C</t>
   </si>
   <si>
-    <t>WARRIORS_PITCH_5C.png</t>
-  </si>
-  <si>
     <t>5D</t>
   </si>
   <si>
-    <t>WARRIORS_PITCH_5D.png</t>
-  </si>
-  <si>
     <t>5E</t>
   </si>
   <si>
-    <t>WARRIORS_PITCH_5E.png</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -223,6 +208,21 @@
   </si>
   <si>
     <t>text_angle</t>
+  </si>
+  <si>
+    <t>WARRIORS_PITCH5A_WHOLE.png</t>
+  </si>
+  <si>
+    <t>WARRIORS_PITCH5B_WHOLE.png</t>
+  </si>
+  <si>
+    <t>WARRIORS_PITCH5C_WHOLE.png</t>
+  </si>
+  <si>
+    <t>WARRIORS_PITCH5D_WHOLE.png</t>
+  </si>
+  <si>
+    <t>WARRIORS_PITCH5E_WHOLE.png</t>
   </si>
 </sst>
 </file>
@@ -628,49 +628,49 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -706,25 +706,25 @@
         <v>23.1</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L2" s="1">
         <v>16.100000000000001</v>
       </c>
       <c r="M2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N2" s="1">
         <v>19.100000000000001</v>
       </c>
       <c r="O2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P2" s="2">
         <v>13.1</v>
       </c>
       <c r="Q2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -778,7 +778,7 @@
         <v>16</v>
       </c>
       <c r="O3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P3" s="2">
         <v>11</v>
@@ -901,7 +901,7 @@
         <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P5" s="2">
         <v>13.5</v>
@@ -959,7 +959,7 @@
         <v>14</v>
       </c>
       <c r="O6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P6" s="2">
         <v>10.7</v>
@@ -1137,7 +1137,7 @@
         <v>16</v>
       </c>
       <c r="O9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P9" s="2">
         <f>P3</f>
@@ -1320,7 +1320,7 @@
         <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P12" s="2" cm="1">
         <f t="array" ref="P12:P13">P9:P10</f>
@@ -1397,7 +1397,7 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1">
         <v>137.1</v>
@@ -1424,13 +1424,13 @@
         <v>10.199999999999999</v>
       </c>
       <c r="K14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L14">
         <v>7.7</v>
       </c>
       <c r="M14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N14">
         <v>8.8000000000000007</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1">
         <v>232.8</v>
@@ -1482,13 +1482,13 @@
         <v>10.199999999999999</v>
       </c>
       <c r="K15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L15">
         <v>7.7</v>
       </c>
       <c r="M15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N15">
         <v>8.8000000000000007</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1">
         <v>328.5</v>
@@ -1540,13 +1540,13 @@
         <v>10.199999999999999</v>
       </c>
       <c r="K16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L16">
         <v>7.7</v>
       </c>
       <c r="M16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N16">
         <v>8.8000000000000007</v>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1">
         <v>173.1</v>
@@ -1597,13 +1597,13 @@
         <v>10.199999999999999</v>
       </c>
       <c r="K17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L17">
         <v>7.7</v>
       </c>
       <c r="M17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N17">
         <v>8.8000000000000007</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1">
         <v>266.8</v>
@@ -1654,13 +1654,13 @@
         <v>10.199999999999999</v>
       </c>
       <c r="K18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L18">
         <v>7.7</v>
       </c>
       <c r="M18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N18">
         <v>8.8000000000000007</v>

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA2A6892-6EE2-460E-8E52-BAF359F83BFE}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80697C2-B8F5-457F-84F0-667216AE1CCF}"/>
   <bookViews>
-    <workbookView xWindow="29040" yWindow="3195" windowWidth="21600" windowHeight="13545" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="17790" yWindow="4050" windowWidth="21600" windowHeight="13545" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
+    <sheet name="opponents" sheetId="2" r:id="rId2"/>
+    <sheet name="teams" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,30 +40,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="187">
   <si>
     <t>pitch_key</t>
   </si>
@@ -223,6 +203,405 @@
   </si>
   <si>
     <t>WARRIORS_PITCH5E_WHOLE.png</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>crest_asset_stem</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Banbury RFC</t>
+  </si>
+  <si>
+    <t>Abbey</t>
+  </si>
+  <si>
+    <t>ABBEY</t>
+  </si>
+  <si>
+    <t>Banbury</t>
+  </si>
+  <si>
+    <t>BANBURY</t>
+  </si>
+  <si>
+    <t>Basingstoke</t>
+  </si>
+  <si>
+    <t>BASINGSTOKE</t>
+  </si>
+  <si>
+    <t>BEACONSFIELD</t>
+  </si>
+  <si>
+    <t>Bracknell</t>
+  </si>
+  <si>
+    <t>BRACKNELL</t>
+  </si>
+  <si>
+    <t>Chinnor</t>
+  </si>
+  <si>
+    <t>CHINNOR</t>
+  </si>
+  <si>
+    <t>CHIPPING NORTON</t>
+  </si>
+  <si>
+    <t>Cirencester</t>
+  </si>
+  <si>
+    <t>CIRENCESTER</t>
+  </si>
+  <si>
+    <t>Cricklade</t>
+  </si>
+  <si>
+    <t>CRICKLADE</t>
+  </si>
+  <si>
+    <t>DNQ</t>
+  </si>
+  <si>
+    <t>ELLINGHAM &amp; RINGWOOD</t>
+  </si>
+  <si>
+    <t>Faringdon</t>
+  </si>
+  <si>
+    <t>FARINGDON</t>
+  </si>
+  <si>
+    <t>Faringdon Festival</t>
+  </si>
+  <si>
+    <t>Faringdon Fest</t>
+  </si>
+  <si>
+    <t>FARINGDON FESTIVAL</t>
+  </si>
+  <si>
+    <t>Farnham</t>
+  </si>
+  <si>
+    <t>FARNHAM</t>
+  </si>
+  <si>
+    <t>Grove</t>
+  </si>
+  <si>
+    <t>GROVE</t>
+  </si>
+  <si>
+    <t>Guernsey</t>
+  </si>
+  <si>
+    <t>GUERNSEY</t>
+  </si>
+  <si>
+    <t>Havant</t>
+  </si>
+  <si>
+    <t>HAVANT</t>
+  </si>
+  <si>
+    <t>Maidenhead</t>
+  </si>
+  <si>
+    <t>MAIDENHEAD</t>
+  </si>
+  <si>
+    <t>Newbury</t>
+  </si>
+  <si>
+    <t>NEWBURY</t>
+  </si>
+  <si>
+    <t>OAKMEDIANS</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>OXFORD</t>
+  </si>
+  <si>
+    <t>Quins</t>
+  </si>
+  <si>
+    <t>OXFORD QUINS</t>
+  </si>
+  <si>
+    <t>Petersfield</t>
+  </si>
+  <si>
+    <t>PETERSFIELD</t>
+  </si>
+  <si>
+    <t>Rams</t>
+  </si>
+  <si>
+    <t>RAMS</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>READING</t>
+  </si>
+  <si>
+    <t>Reading &amp; Abbey</t>
+  </si>
+  <si>
+    <t>READING &amp; ABBEY</t>
+  </si>
+  <si>
+    <t>RWB</t>
+  </si>
+  <si>
+    <t>Salisbury</t>
+  </si>
+  <si>
+    <t>SALISBURY</t>
+  </si>
+  <si>
+    <t>Supermarine</t>
+  </si>
+  <si>
+    <t>SUPERMARINE</t>
+  </si>
+  <si>
+    <t>Swindon</t>
+  </si>
+  <si>
+    <t>SWINDON</t>
+  </si>
+  <si>
+    <t>Roses</t>
+  </si>
+  <si>
+    <t>SWINDON ROSES</t>
+  </si>
+  <si>
+    <t>Swindon Roses Festival</t>
+  </si>
+  <si>
+    <t>Roses Fest</t>
+  </si>
+  <si>
+    <t>SWINDON ROSES FESTIVAL</t>
+  </si>
+  <si>
+    <t>Tadley</t>
+  </si>
+  <si>
+    <t>TADLEY</t>
+  </si>
+  <si>
+    <t>Thatcham</t>
+  </si>
+  <si>
+    <t>THATCHAM</t>
+  </si>
+  <si>
+    <t>Trojans</t>
+  </si>
+  <si>
+    <t>TROJANS</t>
+  </si>
+  <si>
+    <t>Wallingford</t>
+  </si>
+  <si>
+    <t>WALLINGFORD</t>
+  </si>
+  <si>
+    <t>Winchleigh</t>
+  </si>
+  <si>
+    <t>WINCHLEIGH</t>
+  </si>
+  <si>
+    <t>Windsor</t>
+  </si>
+  <si>
+    <t>WINDSOR</t>
+  </si>
+  <si>
+    <t>Worthing</t>
+  </si>
+  <si>
+    <t>WORTHING</t>
+  </si>
+  <si>
+    <t>Worthing Festival</t>
+  </si>
+  <si>
+    <t>Worthing Fest</t>
+  </si>
+  <si>
+    <t>WORTHING FESTIVAL</t>
+  </si>
+  <si>
+    <t>Abbey RFC</t>
+  </si>
+  <si>
+    <t>Basingstoke RFC</t>
+  </si>
+  <si>
+    <t>Beaconsfield RFC</t>
+  </si>
+  <si>
+    <t>Bracknell RFC</t>
+  </si>
+  <si>
+    <t>Chinnor RFC</t>
+  </si>
+  <si>
+    <t>Chipping Norton RFC</t>
+  </si>
+  <si>
+    <t>Cirencester RFC</t>
+  </si>
+  <si>
+    <t>Cricklade RFC</t>
+  </si>
+  <si>
+    <t>Ellingham &amp; Ringwood RFC</t>
+  </si>
+  <si>
+    <t>Faringdon RFC</t>
+  </si>
+  <si>
+    <t>Farnham RFC</t>
+  </si>
+  <si>
+    <t>Grove RFC</t>
+  </si>
+  <si>
+    <t>Guernsey RFC</t>
+  </si>
+  <si>
+    <t>Havant RFC</t>
+  </si>
+  <si>
+    <t>Maidenhead RFC</t>
+  </si>
+  <si>
+    <t>Newbury RFC</t>
+  </si>
+  <si>
+    <t>Oakmeadians RFC</t>
+  </si>
+  <si>
+    <t>Oxford RFC</t>
+  </si>
+  <si>
+    <t>Oxford Quins RFC</t>
+  </si>
+  <si>
+    <t>Petersfield RFC</t>
+  </si>
+  <si>
+    <t>Rams RFC</t>
+  </si>
+  <si>
+    <t>Reading RFC</t>
+  </si>
+  <si>
+    <t>Royal Wootton Bassett RFC</t>
+  </si>
+  <si>
+    <t>Salisbury RFC</t>
+  </si>
+  <si>
+    <t>Supermarine RFC</t>
+  </si>
+  <si>
+    <t>Swindon RFC</t>
+  </si>
+  <si>
+    <t>Tadley RFC</t>
+  </si>
+  <si>
+    <t>Thatcham RFC</t>
+  </si>
+  <si>
+    <t>Trojans RFC</t>
+  </si>
+  <si>
+    <t>Wallingford RFC</t>
+  </si>
+  <si>
+    <t>Windsor RFC</t>
+  </si>
+  <si>
+    <t>Worthing RFC</t>
+  </si>
+  <si>
+    <t>Swindon RFC Roses</t>
+  </si>
+  <si>
+    <t>CN RFC</t>
+  </si>
+  <si>
+    <t>E&amp;R RFC</t>
+  </si>
+  <si>
+    <t>Cotswold Lionesses</t>
+  </si>
+  <si>
+    <t>Lionesses</t>
+  </si>
+  <si>
+    <t>COTSWOLD LIONESSES</t>
+  </si>
+  <si>
+    <t>Oaks RFC</t>
+  </si>
+  <si>
+    <t>R&amp;A</t>
+  </si>
+  <si>
+    <t>RWB RFC</t>
+  </si>
+  <si>
+    <t>Beacs. RFC</t>
+  </si>
+  <si>
+    <t>team_prefix</t>
+  </si>
+  <si>
+    <t>text_primary</t>
+  </si>
+  <si>
+    <t>text_accent</t>
+  </si>
+  <si>
+    <t>DEFAULT</t>
+  </si>
+  <si>
+    <t>WARRIORS</t>
+  </si>
+  <si>
+    <t>#FFE602</t>
+  </si>
+  <si>
+    <t>#F8F9FF</t>
+  </si>
+  <si>
+    <t>#D4AF37</t>
+  </si>
+  <si>
+    <t>#FFFFFF</t>
+  </si>
+  <si>
+    <t>Didcot Newbury Quins</t>
   </si>
 </sst>
 </file>
@@ -269,10 +648,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -618,6 +996,7 @@
     <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="14.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -696,34 +1075,34 @@
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <f>G2</f>
         <v>0</v>
       </c>
       <c r="I2" s="1">
         <v>1.08</v>
       </c>
       <c r="J2" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>45</v>
       </c>
       <c r="L2" s="1">
         <v>16.100000000000001</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="N2" s="1">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="2">
-        <v>13.1</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="P2" s="1">
+        <f>L2</f>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -735,57 +1114,50 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <f>C2</f>
         <v>65.599999999999994</v>
       </c>
       <c r="D3" s="1">
-        <f>D2</f>
         <v>101.5</v>
       </c>
       <c r="E3" s="1">
-        <f>E2/2</f>
         <v>167.9</v>
       </c>
       <c r="F3" s="1">
-        <f>F2</f>
         <v>200.1</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <f>G3</f>
         <v>0</v>
       </c>
       <c r="I3" s="1">
         <v>1.08</v>
       </c>
       <c r="J3" s="1">
-        <v>19.3</v>
-      </c>
-      <c r="K3" t="str">
-        <f>K2</f>
-        <v>Bold</v>
+        <v>21</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="L3" s="1">
         <v>13.5</v>
       </c>
-      <c r="M3" t="str">
-        <f>M2</f>
-        <v>Regular</v>
+      <c r="M3" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="N3" s="1">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="2">
-        <v>11</v>
-      </c>
-      <c r="Q3" t="str">
-        <f>Q2</f>
-        <v>Regular</v>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P18" si="0">L3</f>
+        <v>13.5</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -796,62 +1168,50 @@
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <f>E4+C3</f>
         <v>233.5</v>
       </c>
       <c r="D4" s="1">
-        <f>D3</f>
         <v>101.5</v>
       </c>
       <c r="E4" s="1">
-        <f>E2/2</f>
         <v>167.9</v>
       </c>
       <c r="F4" s="1">
-        <f>F3</f>
         <v>200.1</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <f>G4</f>
         <v>0</v>
       </c>
       <c r="I4" s="1">
         <v>1.08</v>
       </c>
-      <c r="J4" s="2">
-        <f>J3</f>
-        <v>19.3</v>
-      </c>
-      <c r="K4" t="str">
-        <f>K3</f>
-        <v>Bold</v>
-      </c>
-      <c r="L4" s="2">
-        <f>L3</f>
+      <c r="J4" s="1">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="1">
         <v>13.5</v>
       </c>
-      <c r="M4" t="str">
-        <f>M3</f>
-        <v>Regular</v>
-      </c>
-      <c r="N4" s="2">
-        <f>N3</f>
-        <v>16</v>
-      </c>
-      <c r="O4" t="str">
-        <f>O3</f>
-        <v>SemiBold</v>
-      </c>
-      <c r="P4" s="2">
-        <f>P3</f>
-        <v>11</v>
-      </c>
-      <c r="Q4" t="str">
-        <f>Q3</f>
-        <v>Regular</v>
+      <c r="M4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="1">
+        <v>18</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -877,38 +1237,35 @@
         <v>-61.2</v>
       </c>
       <c r="H5" s="1">
-        <f>G5+90</f>
         <v>28.799999999999997</v>
       </c>
       <c r="I5" s="1">
         <v>1.08</v>
       </c>
-      <c r="J5" s="2">
-        <v>21.3</v>
-      </c>
-      <c r="K5" t="str">
-        <f>K4</f>
-        <v>Bold</v>
-      </c>
-      <c r="L5" s="2">
-        <v>15.5</v>
-      </c>
-      <c r="M5" t="str">
-        <f>M4</f>
-        <v>Regular</v>
-      </c>
-      <c r="N5" s="2">
-        <v>18</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="J5" s="1">
+        <v>26</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P5" s="2">
-        <v>13.5</v>
-      </c>
-      <c r="Q5" t="str">
-        <f>Q4</f>
-        <v>Regular</v>
+      <c r="L5" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="1">
+        <v>22</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="0"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -922,7 +1279,6 @@
         <v>451.4</v>
       </c>
       <c r="D6" s="1">
-        <f>D5</f>
         <v>249.7</v>
       </c>
       <c r="E6" s="1">
@@ -935,38 +1291,35 @@
         <v>-61.2</v>
       </c>
       <c r="H6" s="1">
-        <f>G6+90</f>
         <v>28.799999999999997</v>
       </c>
       <c r="I6" s="1">
         <v>1.08</v>
       </c>
-      <c r="J6" s="2">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="K6" t="str">
-        <f>K5</f>
-        <v>Bold</v>
-      </c>
-      <c r="L6">
-        <v>12.1</v>
-      </c>
-      <c r="M6" t="str">
-        <f>M5</f>
-        <v>Regular</v>
-      </c>
-      <c r="N6">
-        <v>14</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="J6" s="1">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="1">
+        <v>18</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P6" s="2">
-        <v>10.7</v>
-      </c>
-      <c r="Q6" t="str">
-        <f>Q5</f>
-        <v>Regular</v>
+      <c r="P6" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -977,14 +1330,12 @@
         <v>14</v>
       </c>
       <c r="C7" s="1">
-        <f>C5</f>
         <v>388.6</v>
       </c>
       <c r="D7" s="1">
         <v>363.9</v>
       </c>
       <c r="E7" s="1">
-        <f>E6</f>
         <v>130.30000000000001</v>
       </c>
       <c r="F7" s="1">
@@ -994,40 +1345,35 @@
         <v>-61.2</v>
       </c>
       <c r="H7" s="1">
-        <f>G7+90</f>
         <v>28.799999999999997</v>
       </c>
       <c r="I7" s="1">
         <v>1.08</v>
       </c>
-      <c r="J7" s="2">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="K7" t="str">
-        <f>K6</f>
-        <v>Bold</v>
-      </c>
-      <c r="L7">
-        <v>12.1</v>
-      </c>
-      <c r="M7" t="str">
-        <f>M6</f>
-        <v>Regular</v>
-      </c>
-      <c r="N7">
-        <v>14</v>
-      </c>
-      <c r="O7" t="str">
-        <f>O6</f>
-        <v>SemiBold</v>
-      </c>
-      <c r="P7" s="2">
-        <f>P6</f>
-        <v>10.7</v>
-      </c>
-      <c r="Q7" t="str">
-        <f>Q6</f>
-        <v>Regular</v>
+      <c r="J7" s="1">
+        <v>21</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="1">
+        <v>18</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1058,30 +1404,30 @@
       <c r="I8" s="1">
         <v>1.08</v>
       </c>
-      <c r="J8" s="2" cm="1">
-        <f t="array" ref="J8:Q8">J5:Q5</f>
-        <v>21.3</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Bold</v>
-      </c>
-      <c r="L8">
-        <v>15.5</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Regular</v>
-      </c>
-      <c r="N8">
-        <v>18</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Bold</v>
-      </c>
-      <c r="P8">
-        <v>13.5</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>Regular</v>
+      <c r="J8" s="1">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="1">
+        <v>22</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="0"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1092,19 +1438,15 @@
         <v>18</v>
       </c>
       <c r="C9" s="1">
-        <f>C8</f>
         <v>80</v>
       </c>
       <c r="D9" s="1">
-        <f>D8</f>
         <v>325.5</v>
       </c>
       <c r="E9" s="1">
-        <f>E8/2</f>
         <v>152.35</v>
       </c>
       <c r="F9" s="1">
-        <f>F8</f>
         <v>194.8</v>
       </c>
       <c r="G9" s="1">
@@ -1116,36 +1458,30 @@
       <c r="I9" s="1">
         <v>1.08</v>
       </c>
-      <c r="J9" s="2">
-        <f>J3</f>
-        <v>19.3</v>
-      </c>
-      <c r="K9" t="str">
-        <f>K8</f>
-        <v>Bold</v>
-      </c>
-      <c r="L9" s="2">
-        <f>L3</f>
+      <c r="J9" s="1">
+        <v>21</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="1">
         <v>13.5</v>
       </c>
-      <c r="M9" t="str">
-        <f>M8</f>
-        <v>Regular</v>
-      </c>
-      <c r="N9" s="2">
-        <f>N3</f>
-        <v>16</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="M9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="1">
+        <v>18</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P9" s="2">
-        <f>P3</f>
-        <v>11</v>
-      </c>
-      <c r="Q9" t="str">
-        <f>Q8</f>
-        <v>Regular</v>
+      <c r="P9" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1156,19 +1492,15 @@
         <v>20</v>
       </c>
       <c r="C10" s="1">
-        <f>E10+C9</f>
         <v>232.35</v>
       </c>
       <c r="D10" s="1">
-        <f>D9</f>
         <v>325.5</v>
       </c>
       <c r="E10" s="1">
-        <f>E8/2</f>
         <v>152.35</v>
       </c>
       <c r="F10" s="1">
-        <f>F9</f>
         <v>194.8</v>
       </c>
       <c r="G10" s="1">
@@ -1180,37 +1512,30 @@
       <c r="I10" s="1">
         <v>1.08</v>
       </c>
-      <c r="J10" s="2">
-        <f>J4</f>
-        <v>19.3</v>
-      </c>
-      <c r="K10" t="str">
-        <f>K9</f>
-        <v>Bold</v>
-      </c>
-      <c r="L10" s="2">
-        <f>L4</f>
+      <c r="J10" s="1">
+        <v>21</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="1">
         <v>13.5</v>
       </c>
-      <c r="M10" t="str">
-        <f>M9</f>
-        <v>Regular</v>
-      </c>
-      <c r="N10" s="2">
-        <f>N4</f>
-        <v>16</v>
-      </c>
-      <c r="O10" t="str">
-        <f>O9</f>
-        <v>SemiBold</v>
-      </c>
-      <c r="P10" s="2">
-        <f>P4</f>
-        <v>11</v>
-      </c>
-      <c r="Q10" t="str">
-        <f>Q9</f>
-        <v>Regular</v>
+      <c r="M10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="1">
+        <v>18</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1241,30 +1566,30 @@
       <c r="I11" s="1">
         <v>1.08</v>
       </c>
-      <c r="J11" s="2" cm="1">
-        <f t="array" ref="J11:Q11">J8:Q8</f>
-        <v>21.3</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Bold</v>
-      </c>
-      <c r="L11">
-        <v>15.5</v>
-      </c>
-      <c r="M11" t="str">
-        <v>Regular</v>
-      </c>
-      <c r="N11">
-        <v>18</v>
-      </c>
-      <c r="O11" t="str">
-        <v>Bold</v>
-      </c>
-      <c r="P11">
-        <v>13.5</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>Regular</v>
+      <c r="J11" s="1">
+        <v>26</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="1">
+        <v>22</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="0"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1275,19 +1600,15 @@
         <v>24</v>
       </c>
       <c r="C12" s="1">
-        <f>C11</f>
         <v>117.3</v>
       </c>
       <c r="D12" s="1">
-        <f>D11</f>
         <v>535.1</v>
       </c>
       <c r="E12" s="1">
-        <f>E11/2</f>
         <v>154.6</v>
       </c>
       <c r="F12" s="1">
-        <f>F11</f>
         <v>191</v>
       </c>
       <c r="G12" s="1">
@@ -1299,36 +1620,30 @@
       <c r="I12" s="1">
         <v>1.08</v>
       </c>
-      <c r="J12" s="2" cm="1">
-        <f t="array" ref="J12:J13">J9:J10</f>
-        <v>19.3</v>
-      </c>
-      <c r="K12" t="str">
-        <f>K11</f>
-        <v>Bold</v>
-      </c>
-      <c r="L12" s="2" cm="1">
-        <f t="array" ref="L12:L13">L9:L10</f>
+      <c r="J12" s="1">
+        <v>21</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="1">
         <v>13.5</v>
       </c>
-      <c r="M12" t="str">
-        <f>M11</f>
-        <v>Regular</v>
-      </c>
-      <c r="N12" s="2" cm="1">
-        <f t="array" ref="N12:N13">N9:N10</f>
-        <v>16</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="M12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="1">
+        <v>18</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P12" s="2" cm="1">
-        <f t="array" ref="P12:P13">P9:P10</f>
-        <v>11</v>
-      </c>
-      <c r="Q12" t="str">
-        <f>Q11</f>
-        <v>Regular</v>
+      <c r="P12" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1339,19 +1654,15 @@
         <v>26</v>
       </c>
       <c r="C13" s="1">
-        <f>E13+C12</f>
         <v>271.89999999999998</v>
       </c>
       <c r="D13" s="1">
-        <f>D12</f>
         <v>535.1</v>
       </c>
       <c r="E13" s="1">
-        <f>E11/2</f>
         <v>154.6</v>
       </c>
       <c r="F13" s="1">
-        <f>F12</f>
         <v>191</v>
       </c>
       <c r="G13" s="1">
@@ -1363,33 +1674,30 @@
       <c r="I13" s="1">
         <v>1.08</v>
       </c>
-      <c r="J13">
-        <v>19.3</v>
-      </c>
-      <c r="K13" t="str">
-        <f>K12</f>
-        <v>Bold</v>
-      </c>
-      <c r="L13">
+      <c r="J13" s="1">
+        <v>21</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="1">
         <v>13.5</v>
       </c>
-      <c r="M13" t="str">
-        <f>M12</f>
-        <v>Regular</v>
-      </c>
-      <c r="N13">
-        <v>16</v>
-      </c>
-      <c r="O13" t="str">
-        <f>O12</f>
-        <v>SemiBold</v>
-      </c>
-      <c r="P13" s="2">
-        <v>11</v>
-      </c>
-      <c r="Q13" t="str">
-        <f>Q12</f>
-        <v>Regular</v>
+      <c r="M13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="1">
+        <v>18</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P13" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1415,36 +1723,35 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I14" s="1">
         <v>1.08</v>
       </c>
-      <c r="J14">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="J14" s="1">
+        <v>18</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L14">
-        <v>7.7</v>
-      </c>
-      <c r="M14" t="s">
-        <v>46</v>
-      </c>
-      <c r="N14">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O14" t="str">
-        <f t="shared" ref="O14:O18" si="0">O13</f>
-        <v>SemiBold</v>
-      </c>
-      <c r="P14">
-        <v>7</v>
-      </c>
-      <c r="Q14" t="str">
-        <f t="shared" ref="Q14:Q18" si="1">Q13</f>
-        <v>Regular</v>
+      <c r="L14" s="1">
+        <v>12</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="1">
+        <v>16</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1458,51 +1765,47 @@
         <v>232.8</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ref="D15:F16" si="2">D14</f>
         <v>748.1</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="2"/>
         <v>85.7</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="2"/>
         <v>125.4</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I15" s="1">
         <v>1.08</v>
       </c>
-      <c r="J15">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="J15" s="1">
+        <v>18</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L15">
-        <v>7.7</v>
-      </c>
-      <c r="M15" t="s">
-        <v>46</v>
-      </c>
-      <c r="N15">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O15" t="str">
+      <c r="L15" s="1">
+        <v>12</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="1">
+        <v>16</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" s="1">
         <f t="shared" si="0"/>
-        <v>SemiBold</v>
-      </c>
-      <c r="P15">
-        <v>7</v>
-      </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="1"/>
-        <v>Regular</v>
+        <v>12</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1516,51 +1819,47 @@
         <v>328.5</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="2"/>
         <v>748.1</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="2"/>
         <v>85.7</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="2"/>
         <v>125.4</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I16" s="1">
         <v>1.08</v>
       </c>
-      <c r="J16">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="J16" s="1">
+        <v>18</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L16">
-        <v>7.7</v>
-      </c>
-      <c r="M16" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O16" t="str">
+      <c r="L16" s="1">
+        <v>12</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="1">
+        <v>16</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P16" s="1">
         <f t="shared" si="0"/>
-        <v>SemiBold</v>
-      </c>
-      <c r="P16">
-        <v>7</v>
-      </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="1"/>
-        <v>Regular</v>
+        <v>12</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1577,47 +1876,44 @@
         <v>883.5</v>
       </c>
       <c r="E17" s="1">
-        <f>E16</f>
         <v>85.7</v>
       </c>
       <c r="F17" s="1">
-        <f>F16</f>
         <v>125.4</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I17" s="1">
         <v>1.08</v>
       </c>
-      <c r="J17">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="J17" s="1">
+        <v>18</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L17">
-        <v>7.7</v>
-      </c>
-      <c r="M17" t="s">
-        <v>46</v>
-      </c>
-      <c r="N17">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O17" t="str">
+      <c r="L17" s="1">
+        <v>12</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="1">
+        <v>16</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P17" s="1">
         <f t="shared" si="0"/>
-        <v>SemiBold</v>
-      </c>
-      <c r="P17">
-        <v>7</v>
-      </c>
-      <c r="Q17" t="str">
-        <f t="shared" si="1"/>
-        <v>Regular</v>
+        <v>12</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1634,47 +1930,567 @@
         <v>883.5</v>
       </c>
       <c r="E18" s="1">
-        <f>E17</f>
         <v>85.7</v>
       </c>
       <c r="F18" s="1">
-        <f>F17</f>
         <v>125.4</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I18" s="1">
         <v>1.08</v>
       </c>
-      <c r="J18">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="J18" s="1">
+        <v>18</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L18">
-        <v>7.7</v>
-      </c>
-      <c r="M18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O18" t="str">
+      <c r="L18" s="1">
+        <v>12</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="1">
+        <v>16</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>SemiBold</v>
-      </c>
-      <c r="P18">
-        <v>7</v>
-      </c>
-      <c r="Q18" t="str">
-        <f t="shared" si="1"/>
-        <v>Regular</v>
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5837B33A-C646-4048-BB46-7ABB988B4ED9}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>161</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C45B62-0327-453D-A1C7-DF2B8CE88C29}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80697C2-B8F5-457F-84F0-667216AE1CCF}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A6E7AD0-BA2A-42D0-B18A-351E51125F7B}"/>
   <bookViews>
-    <workbookView xWindow="17790" yWindow="4050" windowWidth="21600" windowHeight="13545" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="17790" yWindow="4050" windowWidth="21600" windowHeight="13545" activeTab="2" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
     <sheet name="opponents" sheetId="2" r:id="rId2"/>
-    <sheet name="teams" sheetId="3" r:id="rId3"/>
+    <sheet name="comps" sheetId="4" r:id="rId3"/>
+    <sheet name="teams" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="214">
   <si>
     <t>pitch_key</t>
   </si>
@@ -602,6 +603,87 @@
   </si>
   <si>
     <t>Didcot Newbury Quins</t>
+  </si>
+  <si>
+    <t>team_key</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>HURRICANES</t>
+  </si>
+  <si>
+    <t>COLTS</t>
+  </si>
+  <si>
+    <t>WARRIORS U12</t>
+  </si>
+  <si>
+    <t>WARRIORS U14</t>
+  </si>
+  <si>
+    <t>WARRIORS U16</t>
+  </si>
+  <si>
+    <t>OBB</t>
+  </si>
+  <si>
+    <t>BYC</t>
+  </si>
+  <si>
+    <t>PUP</t>
+  </si>
+  <si>
+    <t>HOB</t>
+  </si>
+  <si>
+    <t>Berks KO</t>
+  </si>
+  <si>
+    <t>U16GIRLSNATCUP</t>
+  </si>
+  <si>
+    <t>list_sort</t>
+  </si>
+  <si>
+    <t>comp_name</t>
+  </si>
+  <si>
+    <t>comp_alias</t>
+  </si>
+  <si>
+    <t>Berks Knockout Cup</t>
+  </si>
+  <si>
+    <t>Berks Youth Cup</t>
+  </si>
+  <si>
+    <t>Girls National Cup</t>
   </si>
 </sst>
 </file>
@@ -611,7 +693,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,6 +704,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2453,6 +2541,246 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B104E4-035A-4BFE-8619-B4B38DDC79FD}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C45B62-0327-453D-A1C7-DF2B8CE88C29}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A6E7AD0-BA2A-42D0-B18A-351E51125F7B}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04CE6783-E4FF-4CA9-BF1C-26216786430F}"/>
   <bookViews>
-    <workbookView xWindow="17790" yWindow="4050" windowWidth="21600" windowHeight="13545" activeTab="2" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="23310" yWindow="2115" windowWidth="28155" windowHeight="13545" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="219">
   <si>
     <t>pitch_key</t>
   </si>
@@ -684,6 +684,21 @@
   </si>
   <si>
     <t>Girls National Cup</t>
+  </si>
+  <si>
+    <t>text_info</t>
+  </si>
+  <si>
+    <t>#821C34</t>
+  </si>
+  <si>
+    <t>#AC0753</t>
+  </si>
+  <si>
+    <t>logo_id</t>
+  </si>
+  <si>
+    <t>BKO</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1340,7 @@
         <v>-61.2</v>
       </c>
       <c r="H5" s="1">
-        <v>28.799999999999997</v>
+        <v>28.8</v>
       </c>
       <c r="I5" s="1">
         <v>1.08</v>
@@ -1379,7 +1394,7 @@
         <v>-61.2</v>
       </c>
       <c r="H6" s="1">
-        <v>28.799999999999997</v>
+        <v>28.8</v>
       </c>
       <c r="I6" s="1">
         <v>1.08</v>
@@ -1433,7 +1448,7 @@
         <v>-61.2</v>
       </c>
       <c r="H7" s="1">
-        <v>28.799999999999997</v>
+        <v>28.8</v>
       </c>
       <c r="I7" s="1">
         <v>1.08</v>
@@ -2542,15 +2557,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B104E4-035A-4BFE-8619-B4B38DDC79FD}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>187</v>
       </c>
@@ -2563,8 +2578,11 @@
       <c r="D1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -2572,7 +2590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -2580,7 +2598,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2588,7 +2606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -2596,7 +2614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>192</v>
       </c>
@@ -2604,7 +2622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>193</v>
       </c>
@@ -2612,7 +2630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>194</v>
       </c>
@@ -2620,7 +2638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>195</v>
       </c>
@@ -2633,8 +2651,11 @@
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>196</v>
       </c>
@@ -2647,8 +2668,11 @@
       <c r="D10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>196</v>
       </c>
@@ -2661,8 +2685,11 @@
       <c r="D11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -2675,8 +2702,11 @@
       <c r="D12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>198</v>
       </c>
@@ -2689,8 +2719,11 @@
       <c r="D13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>199</v>
       </c>
@@ -2703,8 +2736,11 @@
       <c r="D14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>200</v>
       </c>
@@ -2717,8 +2753,11 @@
       <c r="D15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>200</v>
       </c>
@@ -2731,8 +2770,11 @@
       <c r="D16">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>200</v>
       </c>
@@ -2745,8 +2787,11 @@
       <c r="D17">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>201</v>
       </c>
@@ -2759,8 +2804,11 @@
       <c r="D18">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>201</v>
       </c>
@@ -2772,6 +2820,9 @@
       </c>
       <c r="D19">
         <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2782,13 +2833,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C45B62-0327-453D-A1C7-DF2B8CE88C29}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>177</v>
       </c>
@@ -2798,8 +2849,11 @@
       <c r="C1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>180</v>
       </c>
@@ -2809,8 +2863,11 @@
       <c r="C2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>181</v>
       </c>
@@ -2819,6 +2876,9 @@
       </c>
       <c r="C3" t="s">
         <v>184</v>
+      </c>
+      <c r="D3" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9FF86C-123C-45BB-8C1C-F5D645F0EA5B}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5540CD87-F0E9-48EE-8DAB-5829EC4E31C7}"/>
   <bookViews>
-    <workbookView xWindow="22335" yWindow="2145" windowWidth="28155" windowHeight="13545" activeTab="3" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="4320" yWindow="4290" windowWidth="28155" windowHeight="15300" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="229">
   <si>
     <t>pitch_key</t>
   </si>
@@ -566,9 +566,6 @@
     <t>Oaks RFC</t>
   </si>
   <si>
-    <t>R&amp;A</t>
-  </si>
-  <si>
     <t>RWB RFC</t>
   </si>
   <si>
@@ -714,6 +711,24 @@
   </si>
   <si>
     <t>text_fg</t>
+  </si>
+  <si>
+    <t>Walcats</t>
+  </si>
+  <si>
+    <t>WALCATS</t>
+  </si>
+  <si>
+    <t>Minety RFC &amp; Cricklade RFC</t>
+  </si>
+  <si>
+    <t>MRFC &amp; CRFC</t>
+  </si>
+  <si>
+    <t>MINETY &amp; CRICKLADE</t>
+  </si>
+  <si>
+    <t>RRFC &amp; ARFC</t>
   </si>
 </sst>
 </file>
@@ -2095,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5837B33A-C646-4048-BB46-7ABB988B4ED9}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
@@ -2152,7 +2167,7 @@
         <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -2215,7 +2230,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
@@ -2394,7 +2409,7 @@
         <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="C27" t="s">
         <v>105</v>
@@ -2405,7 +2420,7 @@
         <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
         <v>106</v>
@@ -2563,6 +2578,28 @@
       </c>
       <c r="C42" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2583,27 +2620,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" t="s">
         <v>209</v>
       </c>
-      <c r="C1" t="s">
-        <v>210</v>
-      </c>
       <c r="D1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -2611,7 +2648,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -2619,7 +2656,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -2627,7 +2664,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -2635,7 +2672,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -2643,7 +2680,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -2651,7 +2688,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -2662,19 +2699,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9">
         <v>50</v>
@@ -2682,19 +2719,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -2702,19 +2739,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F11">
         <v>50</v>
@@ -2722,19 +2759,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F12">
         <v>60</v>
@@ -2742,19 +2779,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F13">
         <v>70</v>
@@ -2762,19 +2799,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F14">
         <v>40</v>
@@ -2782,19 +2819,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F15">
         <v>50</v>
@@ -2802,19 +2839,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F16">
         <v>50</v>
@@ -2822,19 +2859,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -2842,19 +2879,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F18">
         <v>60</v>
@@ -2862,19 +2899,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F19">
         <v>60</v>
@@ -2899,42 +2936,42 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" t="s">
         <v>177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>178</v>
       </c>
-      <c r="C1" t="s">
-        <v>179</v>
-      </c>
       <c r="D1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" t="s">
         <v>222</v>
-      </c>
-      <c r="G1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F2" t="str">
         <f>D2</f>
@@ -2947,19 +2984,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" t="s">
         <v>183</v>
       </c>
-      <c r="C3" t="s">
-        <v>184</v>
-      </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F3" t="str">
         <f>D3</f>
